--- a/02_加值成品/生物/生物7-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物7-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物7-1 生物的演化　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物7-1 生物的演化　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>生物族群隨時間改變的過程是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>漫長時間</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>族群</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>演化</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>逐代增加</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>演變</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>演化的重要證據之一是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>適者生存</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>逐代增加</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>化石</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>記錄</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>提出天擇說的科學家是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>演化</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>適者生存</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>漫長時間</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>達爾文</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>天擇</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>環境選擇適應者稱？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>適者是最適應環境者未必最強</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>有利性狀需世代累積才顯著</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>天擇/適者生存</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>無變異則無可供選擇的差異</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>選擇</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>演化需要多久時間？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>漫長時間</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>化石</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>提供選擇素材</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>長期</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>演化的素材來自？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>達爾文</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>化石</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>變異</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>多樣</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>演化是個體還族群的改變？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>漫長時間</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>演變歷程</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>族群</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>化石</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>世代</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>化石能顯示生物的？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>演化</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>演變歷程</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>達爾文</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>歷史</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>生物族群世代間性狀改變稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>化石</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>沉積岩</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>適者生存</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>演化</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>演變</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>天擇又稱？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>適者生存</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>提供選擇素材</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>逐代增加</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>漫長時間</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>天擇</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物7-1 生物的演化　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物7-1 生物的演化　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>天擇說中適者指？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>長頸者較能取食存活繁殖</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>適者是最適應環境者未必最強</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>顯示生物隨時間變化</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>最能適應環境者</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>適應</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>生物構造相似暗示？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>提供選擇素材</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>達爾文</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>演變歷程</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>共同祖先</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>親緣</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>變異在演化的角色？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>達爾文</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>變異</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>演化</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>提供選擇素材</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>素材</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>有利性狀會如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>演變歷程</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>逐代增加</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>族群</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>抗藥性細菌增加是因為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>改變選擇壓力使不同性狀被保留</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>天擇保留抗藥個體</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>變異提供差異環境選擇適應者累積成演化</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>天擇/適者生存</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>天擇</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>演化是主動追求的嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>提供選擇素材</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>變異</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>化石</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>非主動</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>化石記錄如何支持演化？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>顯示生物隨時間變化</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>改變選擇壓力使不同性狀被保留</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>細菌有變異抗藥者在藥物下存活繁殖逐漸增多</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>育種由人天擇由環境</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>證據</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>環境改變對演化的影響？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>改變選擇方向</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>漫長時間</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>演變歷程</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>族群</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>選擇</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>化石通常保存在哪類岩石？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>演變歷程</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>提供選擇素材</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>沉積岩</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>改變選擇方向</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>化石</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>長頸鹿脖子變長用天擇如何解釋？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>最能適應環境者</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>長頸者較能取食存活繁殖</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>育種由人天擇由環境</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>無變異則無可供選擇的差異</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>天擇</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物7-1 生物的演化　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物7-1 生物的演化　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>用天擇說解釋抗藥性細菌的出現？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>變異提供差異環境選擇適應者累積成演化</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>顯示生物隨時間變化</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>有利性狀需世代累積才顯著</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>細菌有變異抗藥者在藥物下存活繁殖逐漸增多</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>天擇</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何說演化是變異加天擇的結果？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>最能適應環境者</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>改變選擇壓力使不同性狀被保留</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>變異提供差異環境選擇適應者累積成演化</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>長頸者較能取食存活繁殖</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>化石與構造相似性如何佐證演化？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>育種由人天擇由環境</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>最能適應環境者</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>變異提供差異環境選擇適應者累積成演化</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>化石顯示變化順序相似構造顯示共同祖先</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>證據</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>適者生存為何不等於最強壯？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>有利性狀需世代累積才顯著</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>育種由人天擇由環境</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>顯示生物隨時間變化</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>適者是最適應環境者未必最強</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>觀念</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>環境劇變如何影響物種演化方向？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>適者是最適應環境者未必最強</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>長頸者較能取食存活繁殖</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>改變選擇壓力使不同性狀被保留</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>天擇/適者生存</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>變異是演化必要條件的原因？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>最能適應環境者</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>無變異則無可供選擇的差異</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>適者是最適應環境者未必最強</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>有利性狀需世代累積才顯著</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>演化需漫長時間的原因？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>顯示生物隨時間變化</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>天擇保留抗藥個體</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>有利性狀需世代累積才顯著</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>適者是最適應環境者未必最強</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>人為選擇(育種)與天擇的異同？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>無變異則無可供選擇的差異</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>都選擇性狀,一由人一由環境</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>適者是最適應環境者未必最強</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>顯示生物隨時間變化</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何抗生素濫用會加速抗藥菌？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>最能適應環境者</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>變異提供差異環境選擇適應者累積成演化</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>無變異則無可供選擇的差異</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>殺死敏感菌留下抗藥菌繁殖</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>天擇</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>比較人為育種與自然天擇的選擇者？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>育種由人天擇由環境</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>天擇/適者生存</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>適者是最適應環境者未必最強</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>天擇保留抗藥個體</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物7-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物7-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>演變</t>
+          <t>演變過程：整個族群經過很長的時間，一代一代逐漸改變，這個過程就叫演化</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>記錄</t>
+          <t>化石記錄：埋在地層中的古代生物遺跡，能顯示生物如何隨時間慢慢改變</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>天擇</t>
+          <t>達爾文提出：達爾文觀察生物後提出天擇說，解釋生物如何演化</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>選擇</t>
+          <t>適者生存：環境會淘汰不適應的個體，留下比較能適應的個體繼續生存繁殖</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>長期</t>
+          <t>長期累積：演化不是一夕之間發生，而是要經過非常漫長的世代才會明顯</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>多樣</t>
+          <t>變異素材：同一族群的個體彼此本來就有些微差異，這些差異就是演化的材料</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>世代</t>
+          <t>族群改變：演化是指一整群生物世世代代累積的改變，不是單一個體本身改變</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>歷史</t>
+          <t>演變歷程：從不同地層挖出的化石，可以看出生物外形怎麼一步步改變</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>演變</t>
+          <t>演變：生物族群經過許多世代，遺傳性狀逐漸產生改變的過程稱為演化</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>天擇</t>
+          <t>天擇：天擇的概念又稱適者生存，指環境會篩選出比較能適應的個體讓牠們存活繁衍</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>最適應者：適者不是指最強壯，而是指最能適應當下環境並存活繁殖的個體</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>親緣</t>
+          <t>共同祖先：不同生物身上出現相似構造，暗示牠們可能是從同一個祖先演化來的</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>提供素材：族群中個體間的差異，讓環境有不同性狀可以挑選，推動演化</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>逐代增加：對生存有利的性狀，擁有者較容易存活繁殖，這種性狀會愈來愈多</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>天擇</t>
+          <t>天擇保留：用藥後只有本來就具抗藥性的細菌存活繁殖，抗藥細菌比例才變多</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>非主動</t>
+          <t>非主動：生物不會為了想適應而主動改變，演化是變異加上環境淘汰的結果</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>證據</t>
+          <t>支持演化：不同時期地層的化石顯示生物外形隨時間逐漸不同，證明演化存在</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>選擇</t>
+          <t>改變方向：環境條件變了，原本有利的性狀可能不再有利，演化方向也會跟著變</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>化石</t>
+          <t>化石：生物遺骸經過長時間掩埋、礦化，多半保存在沉積岩中，成為研究演化的重要證據</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>天擇</t>
+          <t>天擇：族群中原本脖子長短不一，脖子較長的個體較能吃到高處的葉子，存活與繁殖的機會較大，經過許多世代，脖子長的性狀就逐漸在族群中普遍起來</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>天擇</t>
+          <t>天擇機制：細菌原本就有個體差異，用藥後只有抗藥的存活並大量繁殖，抗藥性因此逐漸普遍</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>兩者合力：先有變異造成個體差異，再由環境天擇留下適應者，長期累積就形成演化</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>證據</t>
+          <t>雙重證據：化石依地層顯示生物隨時間變化的順序，構造相似則暗示物種來自共同祖先</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>觀念</t>
+          <t>適應才是關鍵：能存活下來的不一定體型最大最強，而是最能配合當地環境條件的個體</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>壓力改變：環境突然變化會改變什麼性狀有利，於是天擇保留的性狀也跟著改變</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>必要</t>
+          <t>沒有變異就沒得選：如果族群裡個體都一模一樣，環境就沒有差異可以挑選，演化無從發生</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>時間</t>
+          <t>世代累積：有利性狀要經過非常多代慢慢增加比例，才能讓整個族群看出明顯改變</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>選擇者不同：兩者都是挑選有利性狀留下來，差別在於育種是人挑選，天擇是由自然環境決定</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>天擇</t>
+          <t>天擇：抗生素會殺死對藥物敏感的細菌，但少數原本就帶有抗藥性的細菌能存活下來並大量繁殖，長期濫用抗生素等於持續篩選，加速抗藥性細菌的出現</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：人為育種是由人類依照需求主動挑選具有理想性狀的個體來繁殖;自然天擇則是由環境條件自然篩選出比較適應的個體存活繁衍，兩者的選擇者不同</t>
         </is>
       </c>
     </row>
